--- a/ig/DM-OCTOBRE-2026/CodeSystem-TRE-R344-NiveauExpertise.xlsx
+++ b/ig/DM-OCTOBRE-2026/CodeSystem-TRE-R344-NiveauExpertise.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260730120000</t>
+    <t>20260928120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:00:00+01:00</t>
+    <t>2026-09-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -457,7 +457,7 @@
     <t>52</t>
   </si>
   <si>
-    <t>Autorisation par l’ARS pour la sous-traitance de préparation pharmaceutique</t>
+    <t>Autorisation par l'ARS pour la sous-traitance de préparation pharmaceutique présentant un risque pour la santé</t>
   </si>
   <si>
     <t>53</t>

--- a/ig/DM-OCTOBRE-2026/CodeSystem-TRE-R344-NiveauExpertise.xlsx
+++ b/ig/DM-OCTOBRE-2026/CodeSystem-TRE-R344-NiveauExpertise.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="158">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260928120000</t>
+    <t>20261102120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T12:00:00+01:00</t>
+    <t>2026-11-02T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -476,6 +476,18 @@
   </si>
   <si>
     <t>Accréditation par la Société Française de Recherche en Médecine du Sommeil (SFRMS)</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>Centre expert pied diabétique</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>Centre expert Epileptologie</t>
   </si>
 </sst>
 </file>
@@ -891,7 +903,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1462,6 +1474,30 @@
       </c>
       <c r="D47" s="2"/>
     </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="D48" s="2"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="D49" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
